--- a/public/templates/vendors/vendor_import_template_sample.xlsx
+++ b/public/templates/vendors/vendor_import_template_sample.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:Q6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,6 +446,12 @@
       <c r="O1" t="str">
         <v/>
       </c>
+      <c r="P1" t="str">
+        <v/>
+      </c>
+      <c r="Q1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -493,6 +499,12 @@
       <c r="O2" t="str">
         <v/>
       </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -538,6 +550,12 @@
         <v/>
       </c>
       <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
         <v/>
       </c>
     </row>
@@ -587,6 +605,12 @@
       <c r="O4" t="str">
         <v>Display Order</v>
       </c>
+      <c r="P4" t="str">
+        <v>Show on Member Dashboard</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Allow Service Requests</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -634,6 +658,12 @@
       <c r="O5" t="str">
         <v>100</v>
       </c>
+      <c r="P5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -681,17 +711,23 @@
       <c r="O6" t="str">
         <v>200</v>
       </c>
+      <c r="P6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Yes</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -992,17 +1028,51 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Show on Member Dashboard</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C22" t="str">
+        <v>boolean_yes_no</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Per-event dashboard-display flag. Maps to the governed event_vendors.show_on_member_dashboard field. Blank preserves the existing Event-Vendor value when Stage 5B execution is implemented.</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>Allow Service Requests</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C23" t="str">
+        <v>boolean_yes_no</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Per-event service-request flag. Maps to the governed event_vendors.allow_service_requests field. Blank preserves the existing Event-Vendor value when Stage 5B execution is implemented.</v>
+      </c>
+      <c r="E23" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
         <v>The sample file can be saved as either XLSX or CSV and used as a model.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/vendors/vendor_import_template_sample.xlsx
+++ b/public/templates/vendors/vendor_import_template_sample.xlsx
@@ -782,7 +782,7 @@
         <v>text</v>
       </c>
       <c r="D7" t="str">
-        <v>The vendor's business name. Required. Maps to the canonical Vendor directory's business_name.</v>
+        <v>The vendor's business name. Required. This is the sole identity key the governed import matches against the canonical Vendor directory.</v>
       </c>
       <c r="E7" t="str">
         <v>Sunrise Coach Detailing</v>
@@ -901,7 +901,7 @@
         <v>boolean_yes_no</v>
       </c>
       <c r="D14" t="str">
-        <v>Not yet executable (Stage 5B). Intended to drive the governed admission action for this Event, not a stored column.</v>
+        <v>Yes admits the matched Vendor to this Event through the governed commit (commit_vendor_import_run_row -&gt; admit_vendor_for_event). Blank/No issues no admission instruction -- it never revokes an existing admission.</v>
       </c>
       <c r="E14" t="str">
         <v>Yes</v>
@@ -1037,7 +1037,7 @@
         <v>boolean_yes_no</v>
       </c>
       <c r="D22" t="str">
-        <v>Per-event dashboard-display flag. Maps to the governed event_vendors.show_on_member_dashboard field. Blank preserves the existing Event-Vendor value when Stage 5B execution is implemented.</v>
+        <v>Per-event dashboard-display flag. Maps to the governed event_vendors.show_on_member_dashboard field. Blank preserves the existing Event-Vendor value.</v>
       </c>
       <c r="E22" t="str">
         <v>Yes</v>
@@ -1054,7 +1054,7 @@
         <v>boolean_yes_no</v>
       </c>
       <c r="D23" t="str">
-        <v>Per-event service-request flag. Maps to the governed event_vendors.allow_service_requests field. Blank preserves the existing Event-Vendor value when Stage 5B execution is implemented.</v>
+        <v>Per-event service-request flag. Maps to the governed event_vendors.allow_service_requests field. Blank preserves the existing Event-Vendor value.</v>
       </c>
       <c r="E23" t="str">
         <v>No</v>

--- a/public/templates/vendors/vendor_import_template_sample.xlsx
+++ b/public/templates/vendors/vendor_import_template_sample.xlsx
@@ -402,7 +402,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>FCOC Vendors Import Template - Sample</v>
+        <v>EpicentraX Vendors Import Template - Sample</v>
       </c>
       <c r="B1" t="str">
         <v/>
